--- a/BD - Pontes BA.xlsx
+++ b/BD - Pontes BA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\israe\Meu Drive\04 - PÓS-GRADUAÇÃO\ENG437 - PRÁTICAS CIÊNCIA DE DADOS\Projeto da Disciplina 02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724F0E29-40A0-4D30-93A4-196ED90CCB61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD46299-0D98-4698-B72E-FC6DF33073C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DB_PONTES_BA" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="83">
   <si>
     <t>EDITAL</t>
   </si>
@@ -45,9 +45,6 @@
     <t>ANO</t>
   </si>
   <si>
-    <t>GABARITO</t>
-  </si>
-  <si>
     <t>002-2025 NºBB 1064672</t>
   </si>
   <si>
@@ -117,9 +114,6 @@
     <t>Sátiro Dias, Inhanbupe, BA</t>
   </si>
   <si>
-    <t>COMP_TOTAL (M)</t>
-  </si>
-  <si>
     <t>005-2025 NºBB 1069824</t>
   </si>
   <si>
@@ -205,9 +199,6 @@
   </si>
   <si>
     <t>T_DIAS</t>
-  </si>
-  <si>
-    <t>P/C</t>
   </si>
   <si>
     <t>Impacto / Indicador</t>
@@ -334,6 +325,18 @@
   <si>
     <t>03/03 Pontes sobre o Riacho Alegre</t>
   </si>
+  <si>
+    <t>LARGURA_M</t>
+  </si>
+  <si>
+    <t>GABARITO_M</t>
+  </si>
+  <si>
+    <t>COMP_TOTAL_M</t>
+  </si>
+  <si>
+    <t>P_C</t>
+  </si>
 </sst>
 </file>
 
@@ -343,7 +346,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -608,9 +611,6 @@
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
@@ -623,15 +623,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
@@ -643,7 +634,7 @@
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -660,6 +651,18 @@
     </xf>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -944,7 +947,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.44140625" bestFit="1" customWidth="1"/>
@@ -952,102 +955,104 @@
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
     <col min="6" max="6" width="29.21875" customWidth="1"/>
     <col min="7" max="7" width="38.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.88671875" style="14" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" style="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" style="14" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" style="10" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="10" customWidth="1"/>
     <col min="11" max="11" width="9.33203125" customWidth="1"/>
-    <col min="12" max="12" width="15.5546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.5546875" style="9" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.5546875" customWidth="1"/>
-    <col min="14" max="14" width="14" style="13" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="15" customFormat="1" ht="35.4" customHeight="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:15" s="11" customFormat="1" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N1" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1" s="16"/>
-      <c r="K1" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="N1" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="O1" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="B2">
         <v>2025</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
         <v>24</v>
       </c>
-      <c r="G2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="14">
+      <c r="H2" s="10">
         <v>20</v>
       </c>
-      <c r="I2" s="14">
-        <v>1</v>
-      </c>
-      <c r="J2" s="14">
+      <c r="I2" s="10">
+        <v>1</v>
+      </c>
+      <c r="J2" s="10">
         <v>10</v>
       </c>
       <c r="K2" t="s">
-        <v>70</v>
-      </c>
-      <c r="L2" s="13">
+        <v>67</v>
+      </c>
+      <c r="L2" s="9">
         <v>1943002.36</v>
       </c>
-      <c r="M2" s="14">
+      <c r="M2" s="10">
         <v>180</v>
       </c>
-      <c r="N2" s="13">
-        <f>L2/H2</f>
+      <c r="N2" s="9">
+        <f t="shared" ref="N2:N14" si="0">L2/H2</f>
         <v>97150.118000000002</v>
       </c>
       <c r="O2">
@@ -1055,48 +1060,48 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>2025</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H3" s="14">
+        <v>66</v>
+      </c>
+      <c r="H3" s="10">
         <v>22</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="10">
         <v>3.37</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="10">
         <v>10</v>
       </c>
       <c r="K3" t="s">
-        <v>71</v>
-      </c>
-      <c r="L3" s="13">
+        <v>68</v>
+      </c>
+      <c r="L3" s="9">
         <v>1426937.75</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="10">
         <v>180</v>
       </c>
-      <c r="N3" s="13">
-        <f>L3/H3</f>
+      <c r="N3" s="9">
+        <f t="shared" si="0"/>
         <v>64860.806818181816</v>
       </c>
       <c r="O3">
@@ -1104,48 +1109,48 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>2025</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="14">
+        <v>26</v>
+      </c>
+      <c r="H4" s="10">
         <v>20</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="10">
         <v>3</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="10">
         <v>10</v>
       </c>
       <c r="K4" t="s">
-        <v>73</v>
-      </c>
-      <c r="L4" s="13">
+        <v>70</v>
+      </c>
+      <c r="L4" s="9">
         <v>2783939.67</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4" s="10">
         <v>180</v>
       </c>
-      <c r="N4" s="13">
-        <f>L4/H4</f>
+      <c r="N4" s="9">
+        <f t="shared" si="0"/>
         <v>139196.9835</v>
       </c>
       <c r="O4">
@@ -1153,48 +1158,48 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>2025</v>
       </c>
       <c r="C5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" t="s">
         <v>29</v>
       </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
       <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="10">
         <v>30</v>
       </c>
-      <c r="H5" s="14">
-        <v>30</v>
-      </c>
-      <c r="I5" s="14">
+      <c r="I5" s="10">
         <v>2.5</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="10">
         <v>10.199999999999999</v>
       </c>
       <c r="K5" t="s">
-        <v>73</v>
-      </c>
-      <c r="L5" s="13">
+        <v>70</v>
+      </c>
+      <c r="L5" s="9">
         <v>3534439.27</v>
       </c>
-      <c r="M5" s="14">
+      <c r="M5" s="10">
         <v>240</v>
       </c>
-      <c r="N5" s="13">
-        <f>L5/H5</f>
+      <c r="N5" s="9">
+        <f t="shared" si="0"/>
         <v>117814.64233333334</v>
       </c>
       <c r="O5">
@@ -1202,49 +1207,49 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>2025</v>
       </c>
       <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" t="s">
         <v>33</v>
       </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>35</v>
       </c>
-      <c r="G6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="14">
+      <c r="H6" s="10">
         <v>30</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="10">
         <v>5.8</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="10">
         <v>11.5</v>
       </c>
       <c r="K6" t="s">
-        <v>71</v>
-      </c>
-      <c r="L6" s="13">
+        <v>68</v>
+      </c>
+      <c r="L6" s="9">
         <f>2729912.04+992508.92+27261.13+2124.72+74397.69+9364.31++(453491.4+42052.27+51526.35)*120/270</f>
         <v>4078711.0411111112</v>
       </c>
-      <c r="M6" s="14">
+      <c r="M6" s="10">
         <v>120</v>
       </c>
-      <c r="N6" s="13">
-        <f>L6/H6</f>
+      <c r="N6" s="9">
+        <f t="shared" si="0"/>
         <v>135957.03470370371</v>
       </c>
       <c r="O6">
@@ -1252,50 +1257,50 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>2025</v>
       </c>
       <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" t="s">
         <v>34</v>
       </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>36</v>
       </c>
-      <c r="G7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" s="14">
+      <c r="H7" s="10">
         <v>50</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="10">
         <f>1.65+7.15+1.4</f>
         <v>10.200000000000001</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="10">
         <v>10</v>
       </c>
       <c r="K7" t="s">
-        <v>73</v>
-      </c>
-      <c r="L7" s="13">
+        <v>70</v>
+      </c>
+      <c r="L7" s="9">
         <f>1632262.42+2293695.42+1085980.34+1751.75+51487.05+30489.32+(453491.4+42052.27+51526.35)*150/270</f>
         <v>5399594.0888888892</v>
       </c>
-      <c r="M7" s="14">
+      <c r="M7" s="10">
         <v>150</v>
       </c>
-      <c r="N7" s="13">
-        <f>L7/H7</f>
+      <c r="N7" s="9">
+        <f t="shared" si="0"/>
         <v>107991.88177777779</v>
       </c>
       <c r="O7">
@@ -1303,36 +1308,36 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>2024</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="14">
+        <v>38</v>
+      </c>
+      <c r="H8" s="10">
         <v>44</v>
       </c>
-      <c r="M8" s="14">
+      <c r="M8" s="10">
         <v>210</v>
       </c>
-      <c r="N8" s="13">
-        <f>L8/H8</f>
+      <c r="N8" s="9">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O8">
@@ -1340,93 +1345,93 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>2024</v>
       </c>
       <c r="C9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
         <v>77</v>
       </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>80</v>
-      </c>
       <c r="G9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="14">
+        <v>38</v>
+      </c>
+      <c r="H9" s="10">
         <v>33</v>
       </c>
-      <c r="M9" s="14"/>
-      <c r="N9" s="13">
-        <f>L9/H9</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="M9" s="10"/>
+      <c r="N9" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>2024</v>
       </c>
       <c r="C10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
         <v>78</v>
       </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>81</v>
-      </c>
       <c r="G10" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="14">
+        <v>38</v>
+      </c>
+      <c r="H10" s="10">
         <v>33</v>
       </c>
-      <c r="M10" s="14"/>
-      <c r="N10" s="13">
-        <f>L10/H10</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="M10" s="10"/>
+      <c r="N10" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>2025</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G11" t="s">
-        <v>42</v>
-      </c>
-      <c r="M11" s="14"/>
-      <c r="N11" s="13" t="e">
-        <f>L11/H11</f>
+        <v>40</v>
+      </c>
+      <c r="M11" s="10"/>
+      <c r="N11" s="9" t="e">
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O11">
@@ -1434,34 +1439,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B12">
         <v>2025</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
-      </c>
-      <c r="H12" s="14">
+        <v>51</v>
+      </c>
+      <c r="H12" s="10">
         <v>30</v>
       </c>
-      <c r="M12" s="14"/>
-      <c r="N12" s="13">
-        <f>L12/H12</f>
+      <c r="M12" s="10"/>
+      <c r="N12" s="9">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O12">
@@ -1469,34 +1474,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B13">
         <v>2025</v>
       </c>
       <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" t="s">
         <v>44</v>
       </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>46</v>
-      </c>
       <c r="G13" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="14">
+        <v>45</v>
+      </c>
+      <c r="H13" s="10">
         <v>200</v>
       </c>
-      <c r="M13" s="14"/>
-      <c r="N13" s="13">
-        <f>L13/H13</f>
+      <c r="M13" s="10"/>
+      <c r="N13" s="9">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O13">
@@ -1504,31 +1509,31 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B14">
         <v>2025</v>
       </c>
       <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" t="s">
         <v>48</v>
       </c>
-      <c r="D14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14" t="s">
-        <v>50</v>
-      </c>
-      <c r="M14" s="14"/>
-      <c r="N14" s="13" t="e">
-        <f>L14/H14</f>
+      <c r="M14" s="10"/>
+      <c r="N14" s="9" t="e">
+        <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O14">
@@ -1545,7 +1550,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BDD2A9F-F29A-47CE-A1B8-ADE523F1AAD9}">
   <dimension ref="A1:G67"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="41.77734375" customWidth="1"/>
     <col min="2" max="5" width="17.33203125" customWidth="1"/>
@@ -1553,1019 +1558,1024 @@
     <col min="7" max="7" width="71.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="42" customHeight="1" thickBot="1">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:7" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="E1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="18">
+      <c r="G1" s="20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="14">
         <f>AVERAGE(E3:E7)</f>
         <v>9.1999999999999993</v>
       </c>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3" s="4">
+      <c r="G2" s="20"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="3">
         <v>2</v>
       </c>
-      <c r="C3" s="4">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1</v>
-      </c>
-      <c r="E3" s="19">
+      <c r="C3" s="3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="15">
         <f>B3*C3*D3</f>
         <v>2</v>
       </c>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="G3" s="20"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="3">
         <v>3</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>2</v>
       </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="19">
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="15">
         <f t="shared" ref="E4:E7" si="0">B4*C4*D4</f>
         <v>6</v>
       </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" s="4">
+      <c r="G4" s="20"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="3">
         <v>3</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>3</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>4</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="15">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="3" t="s">
+      <c r="G5" s="20"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G6" s="20"/>
+    </row>
+    <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="5">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1</v>
+      </c>
+      <c r="E7" s="16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G7" s="20"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="4">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="19">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1">
-      <c r="A7" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="6">
-        <v>1</v>
-      </c>
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-      <c r="D7" s="6">
-        <v>1</v>
-      </c>
-      <c r="E7" s="20">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="18">
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="14">
         <f>AVERAGE(E9:E13)</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="4">
+      <c r="G8" s="20"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="3">
         <v>2</v>
       </c>
-      <c r="C9" s="4">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="19">
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="15">
         <f>B9*C9*D9</f>
         <v>2</v>
       </c>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B10" s="4">
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="3">
         <v>3</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>2</v>
       </c>
-      <c r="D10" s="4">
-        <v>1</v>
-      </c>
-      <c r="E10" s="19">
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="15">
         <f t="shared" ref="E10:E13" si="1">B10*C10*D10</f>
         <v>6</v>
       </c>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B11" s="4">
-        <v>1</v>
-      </c>
-      <c r="C11" s="4">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="19">
+      <c r="G10" s="20"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
+      <c r="E11" s="15">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" s="4">
-        <v>1</v>
-      </c>
-      <c r="C12" s="4">
-        <v>1</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
-      <c r="E12" s="19">
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="15">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" ht="15" thickBot="1">
-      <c r="A13" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="6">
-        <v>1</v>
-      </c>
-      <c r="C13" s="6">
-        <v>1</v>
-      </c>
-      <c r="D13" s="6">
-        <v>1</v>
-      </c>
-      <c r="E13" s="20">
+      <c r="G12" s="20"/>
+    </row>
+    <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1</v>
+      </c>
+      <c r="E13" s="16">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="18">
+      <c r="G13" s="20"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="14">
         <f>AVERAGE(E15:E19)</f>
         <v>3.6</v>
       </c>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="4">
+      <c r="G14" s="20"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="3">
         <v>3</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="3">
         <v>2</v>
       </c>
-      <c r="D15" s="4">
-        <v>1</v>
-      </c>
-      <c r="E15" s="19">
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
         <f>B15*C15*D15</f>
         <v>6</v>
       </c>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B16" s="4">
+      <c r="G15" s="20"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="3">
         <v>3</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="3">
         <v>3</v>
       </c>
-      <c r="D16" s="4">
-        <v>1</v>
-      </c>
-      <c r="E16" s="19">
+      <c r="D16" s="3">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
         <f t="shared" ref="E16:E19" si="2">B16*C16*D16</f>
         <v>9</v>
       </c>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" s="4">
-        <v>1</v>
-      </c>
-      <c r="C17" s="4">
-        <v>1</v>
-      </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="E17" s="19">
+      <c r="G16" s="20"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1</v>
+      </c>
+      <c r="E17" s="15">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B18" s="4">
-        <v>1</v>
-      </c>
-      <c r="C18" s="4">
-        <v>1</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="19">
+      <c r="G17" s="20"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" ht="15" thickBot="1">
-      <c r="A19" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B19" s="6">
-        <v>1</v>
-      </c>
-      <c r="C19" s="6">
-        <v>1</v>
-      </c>
-      <c r="D19" s="6">
-        <v>1</v>
-      </c>
-      <c r="E19" s="20">
+      <c r="G18" s="20"/>
+    </row>
+    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="5">
+        <v>1</v>
+      </c>
+      <c r="C19" s="5">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5">
+        <v>1</v>
+      </c>
+      <c r="E19" s="16">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="18">
+      <c r="G19" s="20"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="14">
         <f>AVERAGE(E21:E25)</f>
         <v>2.6</v>
       </c>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B21" s="4">
+      <c r="G20" s="20"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="3">
         <v>3</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="3">
         <v>2</v>
       </c>
-      <c r="D21" s="4">
-        <v>1</v>
-      </c>
-      <c r="E21" s="19">
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
+      <c r="E21" s="15">
         <f>B21*C21*D21</f>
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22" s="4">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="3">
         <v>2</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="3">
         <v>2</v>
       </c>
-      <c r="D22" s="4">
-        <v>1</v>
-      </c>
-      <c r="E22" s="19">
+      <c r="D22" s="3">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
         <f t="shared" ref="E22:E25" si="3">B22*C22*D22</f>
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B23" s="4">
-        <v>1</v>
-      </c>
-      <c r="C23" s="4">
-        <v>1</v>
-      </c>
-      <c r="D23" s="4">
-        <v>1</v>
-      </c>
-      <c r="E23" s="19">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="3">
+        <v>1</v>
+      </c>
+      <c r="C23" s="3">
+        <v>1</v>
+      </c>
+      <c r="D23" s="3">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" s="4">
-        <v>1</v>
-      </c>
-      <c r="C24" s="4">
-        <v>1</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="19">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="3">
+        <v>1</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1</v>
+      </c>
+      <c r="E24" s="15">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15" thickBot="1">
-      <c r="A25" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B25" s="6">
-        <v>1</v>
-      </c>
-      <c r="C25" s="6">
-        <v>1</v>
-      </c>
-      <c r="D25" s="6">
-        <v>1</v>
-      </c>
-      <c r="E25" s="20">
+    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="5">
+        <v>1</v>
+      </c>
+      <c r="C25" s="5">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5">
+        <v>1</v>
+      </c>
+      <c r="E25" s="16">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="18">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="14">
         <f>AVERAGE(E27:E31)</f>
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B27" s="4">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="3">
         <v>2</v>
       </c>
-      <c r="C27" s="4">
-        <v>1</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="E27" s="19">
+      <c r="C27" s="3">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
         <f>B27*C27*D27</f>
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B28" s="4">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="3">
         <v>3</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="3">
         <v>2</v>
       </c>
-      <c r="D28" s="4">
-        <v>1</v>
-      </c>
-      <c r="E28" s="19">
+      <c r="D28" s="3">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
         <f t="shared" ref="E28:E31" si="4">B28*C28*D28</f>
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" s="4">
-        <v>1</v>
-      </c>
-      <c r="C29" s="4">
-        <v>1</v>
-      </c>
-      <c r="D29" s="4">
-        <v>1</v>
-      </c>
-      <c r="E29" s="19">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="3">
+        <v>1</v>
+      </c>
+      <c r="C29" s="3">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B30" s="4">
-        <v>1</v>
-      </c>
-      <c r="C30" s="4">
-        <v>1</v>
-      </c>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="E30" s="19">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="3">
+        <v>1</v>
+      </c>
+      <c r="C30" s="3">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15" thickBot="1">
-      <c r="A31" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B31" s="6">
-        <v>1</v>
-      </c>
-      <c r="C31" s="6">
-        <v>1</v>
-      </c>
-      <c r="D31" s="6">
-        <v>1</v>
-      </c>
-      <c r="E31" s="20">
+    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="5">
+        <v>1</v>
+      </c>
+      <c r="C31" s="5">
+        <v>1</v>
+      </c>
+      <c r="D31" s="5">
+        <v>1</v>
+      </c>
+      <c r="E31" s="16">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="18">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="14">
         <f>AVERAGE(E33:E37)</f>
         <v>3.6</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B33" s="4">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="3">
         <v>3</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="3">
         <v>2</v>
       </c>
-      <c r="D33" s="4">
-        <v>1</v>
-      </c>
-      <c r="E33" s="19">
+      <c r="D33" s="3">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
         <f>B33*C33*D33</f>
         <v>6</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B34" s="4">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" s="3">
         <v>3</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="3">
         <v>3</v>
       </c>
-      <c r="D34" s="4">
-        <v>1</v>
-      </c>
-      <c r="E34" s="19">
+      <c r="D34" s="3">
+        <v>1</v>
+      </c>
+      <c r="E34" s="15">
         <f t="shared" ref="E34:E37" si="5">B34*C34*D34</f>
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B35" s="4">
-        <v>1</v>
-      </c>
-      <c r="C35" s="4">
-        <v>1</v>
-      </c>
-      <c r="D35" s="4">
-        <v>1</v>
-      </c>
-      <c r="E35" s="19">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35" s="3">
+        <v>1</v>
+      </c>
+      <c r="C35" s="3">
+        <v>1</v>
+      </c>
+      <c r="D35" s="3">
+        <v>1</v>
+      </c>
+      <c r="E35" s="15">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B36" s="4">
-        <v>1</v>
-      </c>
-      <c r="C36" s="4">
-        <v>1</v>
-      </c>
-      <c r="D36" s="4">
-        <v>1</v>
-      </c>
-      <c r="E36" s="19">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B36" s="3">
+        <v>1</v>
+      </c>
+      <c r="C36" s="3">
+        <v>1</v>
+      </c>
+      <c r="D36" s="3">
+        <v>1</v>
+      </c>
+      <c r="E36" s="15">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15" thickBot="1">
-      <c r="A37" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B37" s="6">
-        <v>1</v>
-      </c>
-      <c r="C37" s="6">
-        <v>1</v>
-      </c>
-      <c r="D37" s="6">
-        <v>1</v>
-      </c>
-      <c r="E37" s="20">
+    <row r="37" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" s="5">
+        <v>1</v>
+      </c>
+      <c r="C37" s="5">
+        <v>1</v>
+      </c>
+      <c r="D37" s="5">
+        <v>1</v>
+      </c>
+      <c r="E37" s="16">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="18">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="14">
         <f>AVERAGE(E39:E43)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="15">
+        <f>B39*C39*D39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="15">
+        <f t="shared" ref="E40:E43" si="6">B40*C40*D40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="15">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="19">
-        <f>B39*C39*D39</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="15">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="19">
-        <f t="shared" ref="E40:E43" si="6">B40*C40*D40</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="19">
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="16">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="19">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="15" thickBot="1">
-      <c r="A43" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="20">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="7" t="s">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" s="18"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="14">
+        <f>AVERAGE(E45:E49)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="15">
+        <f>B45*C45*D45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="15">
+        <f t="shared" ref="E46:E49" si="7">B46*C46*D46</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="15">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="15">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="16">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="18">
-        <f>AVERAGE(E45:E49)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="14">
+        <f>AVERAGE(E51:E55)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="15">
+        <f>B51*C51*D51</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="15">
+        <f t="shared" ref="E52:E55" si="8">B52*C52*D52</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="15">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="19">
-        <f>B45*C45*D45</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="15">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="19">
-        <f t="shared" ref="E46:E49" si="7">B46*C46*D46</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="19">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="15" thickBot="1">
-      <c r="A49" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
-      <c r="E49" s="20">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="18">
-        <f>AVERAGE(E51:E55)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="16">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="18"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="14">
+        <f>AVERAGE(E57:E61)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="15">
+        <f>B57*C57*D57</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="15">
+        <f t="shared" ref="E58:E61" si="9">B58*C58*D58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="15">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="19">
-        <f>B51*C51*D51</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="15">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="19">
-        <f t="shared" ref="E52:E55" si="8">B52*C52*D52</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="19">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="19">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="15" thickBot="1">
-      <c r="A55" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="20">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="18">
-        <f>AVERAGE(E57:E61)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="16">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B62" s="18"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="14">
+        <f>AVERAGE(E63:E67)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="15">
+        <f>B63*C63*D63</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="15">
+        <f t="shared" ref="E64:E67" si="10">B64*C64*D64</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="19">
-        <f>B57*C57*D57</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="19">
-        <f t="shared" ref="E58:E61" si="9">B58*C58*D58</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="19">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="19">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="15" thickBot="1">
-      <c r="A61" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="20">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B62" s="8"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="18">
-        <f>AVERAGE(E63:E67)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="19">
-        <f>B63*C63*D63</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="19">
-        <f t="shared" ref="E64:E67" si="10">B64*C64*D64</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="19">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="19">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="15" thickBot="1">
-      <c r="A67" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="20">
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="16">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="G1:G20"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A20:D20"/>
     <mergeCell ref="A62:D62"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="A32:D32"/>
@@ -2573,11 +2583,6 @@
     <mergeCell ref="A44:D44"/>
     <mergeCell ref="A50:D50"/>
     <mergeCell ref="A56:D56"/>
-    <mergeCell ref="G1:G20"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A20:D20"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
